--- a/artfynd/A 3854-2024 artfynd.xlsx
+++ b/artfynd/A 3854-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>57531</v>
+        <v>135525471</v>
       </c>
       <c r="B2" t="n">
-        <v>56766</v>
+        <v>79373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100077</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Utter</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lutra lutra</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>härjflån, Dlr</t>
+          <t>Vansbro, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457760</v>
+        <v>457802</v>
       </c>
       <c r="R2" t="n">
-        <v>6705535</v>
+        <v>6705178</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2005-09-22</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2005-09-22</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -754,21 +757,327 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>57531</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56766</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100077</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Utter</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lutra lutra</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>härjflån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>457760</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6705535</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2005-09-22</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2005-09-22</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Sebastian Kirppu</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135525521</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vansbro, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>457610</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6705198</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135525493</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8449</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vansbro, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>457716</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6705097</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3854-2024 artfynd.xlsx
+++ b/artfynd/A 3854-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135525471</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57531</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135525521</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1078,8 +1098,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135525493</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 3854-2024 artfynd.xlsx
+++ b/artfynd/A 3854-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135525471</v>
       </c>
       <c r="B2" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>135525521</v>
       </c>
       <c r="B4" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>135525493</v>
       </c>
       <c r="B5" t="n">
-        <v>8449</v>
+        <v>8450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 3854-2024 artfynd.xlsx
+++ b/artfynd/A 3854-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135525471</v>
       </c>
       <c r="B2" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 3854-2024 artfynd.xlsx
+++ b/artfynd/A 3854-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>57531</v>
+        <v>135525471</v>
       </c>
       <c r="B2" t="n">
-        <v>56766</v>
+        <v>79441</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100077</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Utter</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lutra lutra</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>härjflån, Dlr</t>
+          <t>Vansbro, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457760</v>
+        <v>457802</v>
       </c>
       <c r="R2" t="n">
-        <v>6705535</v>
+        <v>6705178</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2005-09-22</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2005-09-22</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,30 +762,354 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Emma Munters</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Emma Munters</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/135525471</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>57531</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56766</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100077</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Utter</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lutra lutra</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>härjflån, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>457760</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6705535</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2005-09-22</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2005-09-22</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/57531</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135525521</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vansbro, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>457610</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6705198</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135525521</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>135525493</v>
+      </c>
+      <c r="B5" t="n">
+        <v>8450</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vansbro, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>457716</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6705097</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Vansbro</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Järna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Emma Munters</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135525493</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 3854-2024 artfynd.xlsx
+++ b/artfynd/A 3854-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135525471</v>
       </c>
       <c r="B2" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -891,7 +891,7 @@
         <v>135525521</v>
       </c>
       <c r="B4" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>135525493</v>
       </c>
       <c r="B5" t="n">
-        <v>8450</v>
+        <v>8452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 3854-2024 artfynd.xlsx
+++ b/artfynd/A 3854-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135525471</v>
       </c>
       <c r="B2" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
